--- a/isms-core-framework/A.7-physical-controls/isms-a.7.6-7-14-information-media-handling/WKBK/90_workbooks/ISMS-IMP-A.7.14.S3_Equipment_Disposal_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.7-physical-controls/isms-a.7.6-7-14-information-media-handling/WKBK/90_workbooks/ISMS-IMP-A.7.14.S3_Equipment_Disposal_Assessment_20260208.xlsx
@@ -1611,7 +1611,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>NIST 800-88 Purge</t>
+          <t>NIST 800-88 Rev. 2 Purge</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>NIST 800-88 Purge</t>
+          <t>NIST 800-88 Rev. 2 Purge</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
